--- a/setting_2026_06.xlsx
+++ b/setting_2026_06.xlsx
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,6 +1264,24 @@
         <v>10</v>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>soft</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>duty_priority</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>soft</t>
         </is>
@@ -2475,7 +2493,6 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
@@ -2521,7 +2538,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2562,7 +2578,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2603,7 +2618,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2644,7 +2658,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2685,7 +2698,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2726,7 +2738,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2767,7 +2778,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2808,7 +2818,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2849,7 +2858,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2890,7 +2898,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2931,7 +2938,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2972,7 +2978,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3013,7 +3018,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3054,7 +3058,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3095,7 +3098,6 @@
           <t>D1,D2,D3,D4,D6,D7,D5,D8,D9,D10,D11,D12,D13,D14,D15,D16,D17,D18</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3309,13 +3311,6 @@
           <t>委員会</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3398,13 +3393,6 @@
           <t>レセ編集</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3487,13 +3475,6 @@
           <t>レセ送信</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3576,13 +3557,6 @@
           <t>紙レセ</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3665,13 +3639,6 @@
           <t>連記</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3754,13 +3721,6 @@
           <t>労災</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3843,13 +3803,6 @@
           <t>減点</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3932,12 +3885,6 @@
           <t>総括</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>中川</t>
@@ -4025,12 +3972,6 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>亀甲</t>
@@ -4118,12 +4059,6 @@
           <t>返金</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>尾崎</t>
@@ -4211,13 +4146,6 @@
           <t>自賠レセ</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4300,13 +4228,6 @@
           <t>レセ出し</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4389,13 +4310,6 @@
           <t>過誤</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4478,13 +4392,6 @@
           <t>行為別</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4567,13 +4474,6 @@
           <t>返戻</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4656,13 +4556,6 @@
           <t>変換</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4745,13 +4638,6 @@
           <t>減点分析</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4834,13 +4720,6 @@
           <t>未収月報</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4923,13 +4802,6 @@
           <t>在宅</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5012,13 +4884,6 @@
           <t>治験</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5101,13 +4966,6 @@
           <t>委託</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5145,9 +5003,6 @@
           <t>A33</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>A42</t>
@@ -5178,13 +5033,6 @@
           <t>委託集計</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5192,7 +5040,6 @@
           <t>A42</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>A42</t>
@@ -5203,7 +5050,6 @@
           <t>A34</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>A42</t>
@@ -5214,9 +5060,6 @@
           <t>A34</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>A43</t>
@@ -5232,7 +5075,6 @@
           <t>A36</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>A39</t>
@@ -5243,13 +5085,6 @@
           <t>OCR</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5257,7 +5092,6 @@
           <t>A43</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>A43</t>
@@ -5268,7 +5102,6 @@
           <t>A35</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>A43</t>
@@ -5279,10 +5112,6 @@
           <t>A35</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>A42</t>
@@ -5293,7 +5122,6 @@
           <t>A37</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>A40</t>
@@ -5304,34 +5132,18 @@
           <t>公害</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>A36</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>A36</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>A43</t>
@@ -5342,7 +5154,6 @@
           <t>A38</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>A41</t>
@@ -5353,41 +5164,23 @@
           <t>特呼</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>A37</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>A37</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>A39</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>A42</t>
@@ -5398,41 +5191,23 @@
           <t>産科医療</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>A38</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>A38</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>A40</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>A43</t>
@@ -5443,326 +5218,134 @@
           <t>シフト</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>A39</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>A39</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>A41</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>自賠</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>A40</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>A40</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>A42</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>生保</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>A41</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>A41</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>A43</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>介護</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>A42</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>A42</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>訪問看護</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>A43</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>A43</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>一般文書</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>未収</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>減点コピー</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>物品</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>日通</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5865,7 +5448,6 @@
       <c r="D2" t="n">
         <v>830</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>3.5</v>
       </c>
@@ -5895,7 +5477,6 @@
       <c r="D3" t="n">
         <v>830</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>8.5</v>
       </c>
@@ -5925,7 +5506,6 @@
       <c r="D4" t="n">
         <v>830</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>3.5</v>
       </c>
@@ -5955,7 +5535,6 @@
       <c r="D5" t="n">
         <v>830</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>3.5</v>
       </c>
@@ -5985,7 +5564,6 @@
       <c r="D6" t="n">
         <v>830</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>8.5</v>
       </c>
@@ -6015,7 +5593,6 @@
       <c r="D7" t="n">
         <v>830</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>3.5</v>
       </c>
@@ -6045,7 +5622,6 @@
       <c r="D8" t="n">
         <v>830</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>3.5</v>
       </c>
@@ -6075,7 +5651,6 @@
       <c r="D9" t="n">
         <v>830</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>8</v>
       </c>
@@ -6105,7 +5680,6 @@
       <c r="D10" t="n">
         <v>830</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>8</v>
       </c>
@@ -6135,7 +5709,6 @@
       <c r="D11" t="n">
         <v>830</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>8</v>
       </c>
@@ -6165,7 +5738,6 @@
       <c r="D12" t="n">
         <v>830</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>8.5</v>
       </c>
@@ -6195,7 +5767,6 @@
       <c r="D13" t="n">
         <v>830</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>8.5</v>
       </c>
@@ -6225,7 +5796,6 @@
       <c r="D14" t="n">
         <v>830</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>8.5</v>
       </c>
@@ -6255,7 +5825,6 @@
       <c r="D15" t="n">
         <v>830</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
         <v>3.5</v>
       </c>
@@ -6285,7 +5854,6 @@
       <c r="D16" t="n">
         <v>830</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
         <v>3.5</v>
       </c>
@@ -6315,7 +5883,6 @@
       <c r="D17" t="n">
         <v>830</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>3.5</v>
       </c>
@@ -6345,7 +5912,6 @@
       <c r="D18" t="n">
         <v>830</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>8.5</v>
       </c>
@@ -6375,7 +5941,6 @@
       <c r="D19" t="n">
         <v>830</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
@@ -6405,7 +5970,6 @@
       <c r="D20" t="n">
         <v>830</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>3.5</v>
       </c>
@@ -6435,7 +5999,6 @@
       <c r="D21" t="n">
         <v>830</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>8.5</v>
       </c>
@@ -6465,7 +6028,6 @@
       <c r="D22" t="n">
         <v>830</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>3.5</v>
       </c>
@@ -6495,7 +6057,6 @@
       <c r="D23" t="n">
         <v>830</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
         <v>3.5</v>
       </c>
@@ -6525,7 +6086,6 @@
       <c r="D24" t="n">
         <v>830</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
         <v>8</v>
       </c>
@@ -6555,7 +6115,6 @@
       <c r="D25" t="n">
         <v>830</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
         <v>8</v>
       </c>
@@ -6585,7 +6144,6 @@
       <c r="D26" t="n">
         <v>830</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
         <v>8</v>
       </c>
@@ -6615,7 +6173,6 @@
       <c r="D27" t="n">
         <v>830</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>8.5</v>
       </c>
@@ -6645,7 +6202,6 @@
       <c r="D28" t="n">
         <v>830</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>8.5</v>
       </c>
@@ -6675,7 +6231,6 @@
       <c r="D29" t="n">
         <v>830</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
         <v>8.5</v>
       </c>
@@ -6705,7 +6260,6 @@
       <c r="D30" t="n">
         <v>830</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
         <v>3.5</v>
       </c>
@@ -6735,7 +6289,6 @@
       <c r="D31" t="n">
         <v>830</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
         <v>3.5</v>
       </c>
@@ -6765,7 +6318,6 @@
       <c r="D32" t="n">
         <v>830</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
         <v>3.5</v>
       </c>
@@ -6795,7 +6347,6 @@
       <c r="D33" t="n">
         <v>830</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>8.5</v>
       </c>
@@ -6825,7 +6376,6 @@
       <c r="D34" t="n">
         <v>830</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>3.5</v>
       </c>
@@ -6855,7 +6405,6 @@
       <c r="D35" t="n">
         <v>830</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>3.5</v>
       </c>
@@ -6885,7 +6434,6 @@
       <c r="D36" t="n">
         <v>830</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>8.5</v>
       </c>
@@ -6915,7 +6463,6 @@
       <c r="D37" t="n">
         <v>830</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>3.5</v>
       </c>
@@ -6945,7 +6492,6 @@
       <c r="D38" t="n">
         <v>830</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
         <v>3.5</v>
       </c>
@@ -6975,7 +6521,6 @@
       <c r="D39" t="n">
         <v>830</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>8</v>
       </c>
@@ -7005,7 +6550,6 @@
       <c r="D40" t="n">
         <v>830</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>8</v>
       </c>
@@ -7035,7 +6579,6 @@
       <c r="D41" t="n">
         <v>830</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
         <v>8</v>
       </c>
@@ -7065,7 +6608,6 @@
       <c r="D42" t="n">
         <v>830</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>8.5</v>
       </c>
@@ -7095,7 +6637,6 @@
       <c r="D43" t="n">
         <v>830</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
         <v>8.5</v>
       </c>
@@ -7125,7 +6666,6 @@
       <c r="D44" t="n">
         <v>830</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>8.5</v>
       </c>
@@ -7155,7 +6695,6 @@
       <c r="D45" t="n">
         <v>830</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>3.5</v>
       </c>
@@ -7185,7 +6724,6 @@
       <c r="D46" t="n">
         <v>830</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
         <v>3.5</v>
       </c>
@@ -7215,7 +6753,6 @@
       <c r="D47" t="n">
         <v>830</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
         <v>3.5</v>
       </c>
@@ -7245,7 +6782,6 @@
       <c r="D48" t="n">
         <v>830</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
         <v>8.5</v>
       </c>
@@ -7275,7 +6811,6 @@
       <c r="D49" t="n">
         <v>830</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
         <v>3.5</v>
       </c>
@@ -7305,7 +6840,6 @@
       <c r="D50" t="n">
         <v>830</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
         <v>3.5</v>
       </c>
@@ -7335,7 +6869,6 @@
       <c r="D51" t="n">
         <v>830</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
         <v>8.5</v>
       </c>
@@ -7365,7 +6898,6 @@
       <c r="D52" t="n">
         <v>830</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
         <v>3.5</v>
       </c>
@@ -7395,7 +6927,6 @@
       <c r="D53" t="n">
         <v>830</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>3.5</v>
       </c>
@@ -7425,7 +6956,6 @@
       <c r="D54" t="n">
         <v>830</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>8</v>
       </c>
@@ -7455,7 +6985,6 @@
       <c r="D55" t="n">
         <v>830</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
         <v>8</v>
       </c>
@@ -7485,7 +7014,6 @@
       <c r="D56" t="n">
         <v>830</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>8</v>
       </c>
@@ -7515,7 +7043,6 @@
       <c r="D57" t="n">
         <v>830</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
         <v>8.5</v>
       </c>
@@ -7545,7 +7072,6 @@
       <c r="D58" t="n">
         <v>830</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>8.5</v>
       </c>
@@ -7575,7 +7101,6 @@
       <c r="D59" t="n">
         <v>830</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>8.5</v>
       </c>
@@ -7605,7 +7130,6 @@
       <c r="D60" t="n">
         <v>830</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>3.5</v>
       </c>
@@ -7635,7 +7159,6 @@
       <c r="D61" t="n">
         <v>830</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
         <v>3.5</v>
       </c>
@@ -7665,7 +7188,6 @@
       <c r="D62" t="n">
         <v>830</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>3.5</v>
       </c>
@@ -7695,7 +7217,6 @@
       <c r="D63" t="n">
         <v>830</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
         <v>8.5</v>
       </c>
@@ -7725,7 +7246,6 @@
       <c r="D64" t="n">
         <v>830</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="n">
         <v>3.5</v>
       </c>
@@ -7755,7 +7275,6 @@
       <c r="D65" t="n">
         <v>830</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>3.5</v>
       </c>
@@ -7785,7 +7304,6 @@
       <c r="D66" t="n">
         <v>830</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
         <v>8.5</v>
       </c>
@@ -7815,7 +7333,6 @@
       <c r="D67" t="n">
         <v>830</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
         <v>3.5</v>
       </c>
@@ -7845,7 +7362,6 @@
       <c r="D68" t="n">
         <v>830</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
         <v>3.5</v>
       </c>
@@ -7875,7 +7391,6 @@
       <c r="D69" t="n">
         <v>830</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
         <v>8</v>
       </c>
@@ -7905,7 +7420,6 @@
       <c r="D70" t="n">
         <v>830</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
         <v>8</v>
       </c>
@@ -7935,7 +7449,6 @@
       <c r="D71" t="n">
         <v>830</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
         <v>8</v>
       </c>
@@ -7965,7 +7478,6 @@
       <c r="D72" t="n">
         <v>830</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
         <v>8.5</v>
       </c>
@@ -7995,7 +7507,6 @@
       <c r="D73" t="n">
         <v>830</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
         <v>8.5</v>
       </c>
@@ -8025,7 +7536,6 @@
       <c r="D74" t="n">
         <v>830</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
         <v>8.5</v>
       </c>
@@ -8055,7 +7565,6 @@
       <c r="D75" t="n">
         <v>830</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
         <v>3.5</v>
       </c>
@@ -8085,7 +7594,6 @@
       <c r="D76" t="n">
         <v>830</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
         <v>3.5</v>
       </c>
@@ -8115,7 +7623,6 @@
       <c r="D77" t="n">
         <v>830</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
         <v>3.5</v>
       </c>
@@ -8145,7 +7652,6 @@
       <c r="D78" t="n">
         <v>830</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
         <v>3.5</v>
       </c>
@@ -8175,7 +7681,6 @@
       <c r="D79" t="n">
         <v>830</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>3.5</v>
       </c>
@@ -8205,7 +7710,6 @@
       <c r="D80" t="n">
         <v>830</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>3.5</v>
       </c>
@@ -8235,7 +7739,6 @@
       <c r="D81" t="n">
         <v>830</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="n">
         <v>3.5</v>
       </c>
@@ -8265,7 +7768,6 @@
       <c r="D82" t="n">
         <v>830</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
         <v>3.5</v>
       </c>
@@ -8295,7 +7797,6 @@
       <c r="D83" t="n">
         <v>830</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
         <v>3.5</v>
       </c>
@@ -8325,7 +7826,6 @@
       <c r="D84" t="n">
         <v>830</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
         <v>3.5</v>
       </c>
@@ -8355,7 +7855,6 @@
       <c r="D85" t="n">
         <v>830</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
         <v>3.5</v>
       </c>
@@ -8385,7 +7884,6 @@
       <c r="D86" t="n">
         <v>830</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>3.5</v>
       </c>
@@ -8415,7 +7913,6 @@
       <c r="D87" t="n">
         <v>830</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
         <v>3.5</v>
       </c>
@@ -8445,7 +7942,6 @@
       <c r="D88" t="n">
         <v>830</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
         <v>3.5</v>
       </c>
@@ -8475,7 +7971,6 @@
       <c r="D89" t="n">
         <v>830</v>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
         <v>3.5</v>
       </c>
@@ -8505,7 +8000,6 @@
       <c r="D90" t="n">
         <v>830</v>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
         <v>3.5</v>
       </c>
@@ -8535,7 +8029,6 @@
       <c r="D91" t="n">
         <v>830</v>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="n">
         <v>3.5</v>
       </c>
@@ -8996,7 +8489,6 @@
           <t>ばんたね１</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9009,7 +8501,6 @@
           <t>ばんたね２</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9022,7 +8513,6 @@
           <t>ばんたね３</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9035,7 +8525,6 @@
           <t>ばんたね４</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9048,7 +8537,6 @@
           <t>ばんたね５</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9061,7 +8549,6 @@
           <t>ばんたね６</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9074,7 +8561,6 @@
           <t>ばんたね７</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9087,7 +8573,6 @@
           <t>ばんたね８</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9100,7 +8585,6 @@
           <t>ばんたね９</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9113,7 +8597,6 @@
           <t>ばんたね１０</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9126,7 +8609,6 @@
           <t>ばんたね１１</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9139,7 +8621,6 @@
           <t>ばんたね１２</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9152,7 +8633,6 @@
           <t>ばんたね１３</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9165,7 +8645,6 @@
           <t>ばんたね１４</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9178,7 +8657,6 @@
           <t>ばんたね１５</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/setting_2026_06.xlsx
+++ b/setting_2026_06.xlsx
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,6 +1282,24 @@
         <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
+        <is>
+          <t>soft</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dummy</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>soft</t>
         </is>
